--- a/Archivio/Setup/finalizzatest.xlsx
+++ b/Archivio/Setup/finalizzatest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A5D1E0-5B1A-412E-8366-FE574BEF91DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD27EF9-9C6A-4B87-88E1-BB31001B93CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A102AAA2-C1DC-414C-A2A2-5FEF7C813A2A}"/>
   </bookViews>
@@ -56,9 +56,6 @@
     <t>01_tabella_data</t>
   </si>
   <si>
-    <t>PV_TotalData</t>
-  </si>
-  <si>
     <t>pv_total</t>
   </si>
   <si>
@@ -96,6 +93,9 @@
   </si>
   <si>
     <t>REN</t>
+  </si>
+  <si>
+    <t>PVTotalData</t>
   </si>
 </sst>
 </file>
@@ -495,192 +495,192 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Archivio/Setup/finalizzatest.xlsx
+++ b/Archivio/Setup/finalizzatest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD27EF9-9C6A-4B87-88E1-BB31001B93CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0FD9A0-1A65-4175-B619-8A27FB42D8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A102AAA2-C1DC-414C-A2A2-5FEF7C813A2A}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A102AAA2-C1DC-414C-A2A2-5FEF7C813A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="21">
   <si>
     <t>Azione</t>
   </si>
@@ -92,10 +92,13 @@
     <t>timesheet_information_by_month</t>
   </si>
   <si>
-    <t>REN</t>
-  </si>
-  <si>
     <t>PVTotalData</t>
+  </si>
+  <si>
+    <t>UPTD</t>
+  </si>
+  <si>
+    <t>DateId</t>
   </si>
 </sst>
 </file>
@@ -509,7 +512,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -617,13 +620,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
@@ -634,11 +637,14 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
       <c r="D9" t="s">
         <v>13</v>
       </c>
@@ -651,13 +657,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
@@ -668,13 +677,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>

--- a/Archivio/Setup/finalizzatest.xlsx
+++ b/Archivio/Setup/finalizzatest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0FD9A0-1A65-4175-B619-8A27FB42D8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73EA4576-5BED-46D7-B9BC-86FFDB8D6D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A102AAA2-C1DC-414C-A2A2-5FEF7C813A2A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A102AAA2-C1DC-414C-A2A2-5FEF7C813A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="21">
   <si>
     <t>Azione</t>
   </si>
@@ -476,7 +476,7 @@
     <col min="2" max="2" width="41.28515625" customWidth="1"/>
     <col min="3" max="3" width="27.85546875" customWidth="1"/>
     <col min="4" max="4" width="39.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="5" max="5" width="37.28515625" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="16.5703125" customWidth="1"/>
   </cols>
@@ -646,7 +646,10 @@
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -666,7 +669,10 @@
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
